--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19083,7 +19083,7 @@
           <t>A | 512呎 (3房)
 $1485万
 $29,000/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -19107,7 +19107,7 @@
           <t>D | 392呎 (2房)
 $744万
 $18,974/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -19115,7 +19115,7 @@
           <t>E | 391呎 (2房)
 $725万
 $18,550/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -19123,7 +19123,7 @@
           <t>F | 400呎 (2房)
 $702万
 $17,562/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -19131,7 +19131,7 @@
           <t>G | 469呎 (2房)
 $1079万
 $23,000/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -19139,7 +19139,7 @@
           <t>H | 385呎 (2房)
 $887万
 $23,039/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -19186,7 +19186,7 @@
           <t>D | 392呎 (2房)
 $736万
 $18,783/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -19194,7 +19194,7 @@
           <t>E | 391呎 (2房)
 $703万
 $17,974/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -19202,7 +19202,7 @@
           <t>F | 400呎 (2房)
 $689万
 $17,220/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -19210,7 +19210,7 @@
           <t>G | 469呎 (2房)
 $844万
 $18,000/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -19218,7 +19218,7 @@
           <t>H | 385呎 (2房)
 $821万
 $21,330/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -19265,7 +19265,7 @@
           <t>D | 392呎 (2房)
 $729万
 $18,594/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -19273,7 +19273,7 @@
           <t>E | 391呎 (2房)
 $701万
 $17,921/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -19281,7 +19281,7 @@
           <t>F | 400呎 (2房)
 $687万
 $17,168/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -19289,7 +19289,7 @@
           <t>G | 469呎 (2房)
 $832万
 $17,731/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -19297,7 +19297,7 @@
           <t>H | 385呎 (2房)
 $852万
 $22,143/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -19344,7 +19344,7 @@
           <t>D | 392呎 (2房)
 $722万
 $18,406/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -19360,7 +19360,7 @@
           <t>F | 400呎 (2房)
 $685万
 $17,118/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -19368,7 +19368,7 @@
           <t>G | 469呎 (2房)
 $819万
 $17,465/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -19376,7 +19376,7 @@
           <t>H | 385呎 (2房)
 $789万
 $20,501/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -19407,7 +19407,7 @@
           <t>B | 374呎 (2房)
 $885万
 $23,663/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -19423,7 +19423,7 @@
           <t>D | 392呎 (2房)
 $721万
 $18,403/呎
-(24年-09月-02日)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -19431,7 +19431,7 @@
           <t>E | 391呎 (2房)
 $697万
 $17,816/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -19439,7 +19439,7 @@
           <t>F | 400呎 (2房)
 $683万
 $17,065/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -19447,7 +19447,7 @@
           <t>G | 469呎 (2房)
 $817万
 $17,416/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -19455,7 +19455,7 @@
           <t>H | 385呎 (2房)
 $742万
 $19,286/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -19463,7 +19463,7 @@
           <t>J | 384呎 (2房)
 $752万
 $19,578/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -19486,7 +19486,7 @@
           <t>B | 374呎 (2房)
 $868万
 $23,201/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -19494,7 +19494,7 @@
           <t>C | 560呎 (3房)
 $1301万
 $23,234/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -19502,7 +19502,7 @@
           <t>D | 392呎 (2房)
 $709万
 $18,077/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -19510,7 +19510,7 @@
           <t>E | 391呎 (2房)
 $694万
 $17,762/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -19526,7 +19526,7 @@
           <t>G | 469呎 (2房)
 $807万
 $17,215/呎
-(24年-09月-09日)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -19534,7 +19534,7 @@
           <t>H | 385呎 (2房)
 $736万
 $19,130/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -19542,7 +19542,7 @@
           <t>J | 384呎 (2房)
 $746万
 $19,422/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19557,7 @@
           <t>A | 512呎 (3房)
 $1148万
 $22,430/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -19565,7 +19565,7 @@
           <t>B | 374呎 (2房)
 $826万
 $22,096/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -19573,7 +19573,7 @@
           <t>C | 560呎 (3房)
 $1239万
 $22,129/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -19581,7 +19581,7 @@
           <t>D | 392呎 (2房)
 $737万
 $18,793/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -19589,7 +19589,7 @@
           <t>E | 391呎 (2房)
 $692万
 $17,711/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -19597,7 +19597,7 @@
           <t>F | 400呎 (2房)
 $679万
 $16,965/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -19605,7 +19605,7 @@
           <t>G | 469呎 (2房)
 $796万
 $16,962/呎
-(24年-09月-09日)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -19613,7 +19613,7 @@
           <t>H | 385呎 (2房)
 $731万
 $18,977/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -19621,7 +19621,7 @@
           <t>J | 384呎 (2房)
 $740万
 $19,266/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
           <t>A | 512呎 (3房)
 $1098万
 $21,451/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19644,7 +19644,7 @@
           <t>B | 374呎 (2房)
 $821万
 $21,941/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -19652,7 +19652,7 @@
           <t>C | 560呎 (3房)
 $1230万
 $21,973/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -19660,7 +19660,7 @@
           <t>D | 392呎 (2房)
 $734万
 $18,735/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -19668,7 +19668,7 @@
           <t>E | 391呎 (2房)
 $690万
 $17,655/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -19676,7 +19676,7 @@
           <t>F | 400呎 (2房)
 $706万
 $17,638/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -19684,7 +19684,7 @@
           <t>G | 469呎 (2房)
 $791万
 $16,859/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -19692,7 +19692,7 @@
           <t>H | 385呎 (2房)
 $725万
 $18,823/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -19700,7 +19700,7 @@
           <t>J | 384呎 (2房)
 $734万
 $19,109/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -19715,7 +19715,7 @@
           <t>A | 512呎 (3房)
 $1086万
 $21,215/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -19723,7 +19723,7 @@
           <t>B | 374呎 (2房)
 $812万
 $21,706/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -19731,7 +19731,7 @@
           <t>C | 560呎 (3房)
 $1204万
 $21,507/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -19739,7 +19739,7 @@
           <t>D | 392呎 (2房)
 $719万
 $18,349/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -19747,7 +19747,7 @@
           <t>E | 391呎 (2房)
 $705万
 $18,031/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -19755,7 +19755,7 @@
           <t>F | 400呎 (2房)
 $674万
 $16,862/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -19763,7 +19763,7 @@
           <t>G | 469呎 (2房)
 $792万
 $16,876/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -19771,7 +19771,7 @@
           <t>H | 385呎 (2房)
 $732万
 $19,003/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -19779,7 +19779,7 @@
           <t>J | 384呎 (2房)
 $728万
 $18,956/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19794,7 @@
           <t>A | 512呎 (3房)
 $1074万
 $20,980/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -19802,7 +19802,7 @@
           <t>B | 374呎 (2房)
 $803万
 $21,468/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -19810,7 +19810,7 @@
           <t>C | 560呎 (3房)
 $1191万
 $21,271/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -19818,7 +19818,7 @@
           <t>D | 392呎 (2房)
 $700万
 $17,860/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -19826,7 +19826,7 @@
           <t>E | 391呎 (2房)
 $686万
 $17,550/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -19834,7 +19834,7 @@
           <t>F | 400呎 (2房)
 $672万
 $16,812/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -19842,7 +19842,7 @@
           <t>G | 469呎 (2房)
 $790万
 $16,836/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -19850,7 +19850,7 @@
           <t>H | 385呎 (2房)
 $713万
 $18,519/呎
-(25年-06月-04日)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -19858,7 +19858,7 @@
           <t>J | 384呎 (2房)
 $722万
 $18,799/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
           <t>A | 512呎 (3房)
 $1062万
 $20,750/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -19881,7 +19881,7 @@
           <t>B | 374呎 (2房)
 $794万
 $21,233/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -19889,7 +19889,7 @@
           <t>C | 560呎 (3房)
 $1178万
 $21,036/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -19897,7 +19897,7 @@
           <t>D | 392呎 (2房)
 $745万
 $19,000/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -19905,7 +19905,7 @@
           <t>E | 391呎 (2房)
 $684万
 $17,499/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>F | 400呎 (2房)
 $670万
 $16,762/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -19921,7 +19921,7 @@
           <t>G | 469呎 (2房)
 $788万
 $16,793/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -19929,7 +19929,7 @@
           <t>H | 385呎 (2房)
 $707万
 $18,369/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -19937,7 +19937,7 @@
           <t>J | 384呎 (2房)
 $716万
 $18,651/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
           <t>A | 512呎 (3房)
 $1046万
 $20,439/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>B | 374呎 (2房)
 $780万
 $20,845/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>C | 560呎 (3房)
 $1173万
 $20,952/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>D | 392呎 (2房)
 $696万
 $17,755/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -19984,7 +19984,7 @@
           <t>E | 391呎 (2房)
 $682万
 $17,445/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -19992,7 +19992,7 @@
           <t>F | 400呎 (2房)
 $697万
 $17,425/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -20000,7 +20000,7 @@
           <t>G | 469呎 (2房)
 $819万
 $17,467/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -20008,7 +20008,7 @@
           <t>H | 385呎 (2房)
 $714万
 $18,553/呎
-(24年-09月-03日)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -20016,7 +20016,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,500/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
           <t>A | 512呎 (3房)
 $1039万
 $20,285/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>B | 374呎 (2房)
 $771万
 $20,610/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>C | 560呎 (3房)
 $1159万
 $20,693/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>D | 392呎 (2房)
 $694万
 $17,702/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>E | 391呎 (2房)
 $680万
 $17,394/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>F | 400呎 (2房)
 $695万
 $17,375/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>G | 469呎 (2房)
 $784万
 $16,710/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -20087,7 +20087,7 @@
           <t>H | 385呎 (2房)
 $706万
 $18,332/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -20095,7 +20095,7 @@
           <t>J | 384呎 (2房)
 $829万
 $21,586/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -20110,7 +20110,7 @@
           <t>A | 512呎 (3房)
 $1072万
 $20,941/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>B | 374呎 (2房)
 $763万
 $20,406/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>C | 560呎 (3房)
 $1142万
 $20,388/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>D | 392呎 (2房)
 $643万
 $16,393/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>E | 391呎 (2房)
 $678万
 $17,343/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>F | 400呎 (2房)
 $664万
 $16,612/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>G | 469呎 (2房)
 $782万
 $16,670/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>H | 385呎 (2房)
 $704万
 $18,278/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>J | 384呎 (2房)
 $712万
 $18,555/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -20197,7 +20197,7 @@
           <t>B | 374呎 (2房)
 $784万
 $20,965/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>C | 560呎 (3房)
 $1122万
 $20,036/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>D | 392呎 (2房)
 $690万
 $17,594/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>E | 391呎 (2房)
 $676万
 $17,292/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>F | 400呎 (2房)
 $691万
 $17,270/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>G | 469呎 (2房)
 $780万
 $16,625/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>H | 385呎 (2房)
 $732万
 $19,003/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -20253,7 +20253,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,497/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
           <t>A | 512呎 (3房)
 $1001万
 $19,553/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -20276,7 +20276,7 @@
           <t>B | 374呎 (2房)
 $779万
 $20,818/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20284,7 +20284,7 @@
           <t>C | 560呎 (3房)
 $1162万
 $20,746/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -20292,7 +20292,7 @@
           <t>D | 392呎 (2房)
 $680万
 $17,337/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -20300,7 +20300,7 @@
           <t>E | 391呎 (2房)
 $663万
 $16,951/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>F | 400呎 (2房)
 $689万
 $17,215/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>G | 469呎 (2房)
 $811万
 $17,292/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>H | 385呎 (2房)
 $729万
 $18,945/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -20332,7 +20332,7 @@
           <t>J | 384呎 (2房)
 $708万
 $18,443/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -20347,7 +20347,7 @@
           <t>A | 512呎 (3房)
 $1018万
 $19,893/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -20355,7 +20355,7 @@
           <t>B | 374呎 (2房)
 $742万
 $19,826/呎
-(24年-07月-30日)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -20363,7 +20363,7 @@
           <t>C | 560呎 (3房)
 $1106万
 $19,757/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -20371,7 +20371,7 @@
           <t>D | 392呎 (2房)
 $682万
 $17,411/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -20379,7 +20379,7 @@
           <t>E | 391呎 (2房)
 $672万
 $17,192/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -20387,7 +20387,7 @@
           <t>F | 400呎 (2房)
 $658万
 $16,462/呎
-(24年-07月-29日)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -20395,7 +20395,7 @@
           <t>G | 469呎 (2房)
 $828万
 $17,655/呎
-(24年-07月-29日)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -20403,7 +20403,7 @@
           <t>H | 385呎 (2房)
 $698万
 $18,117/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -20411,7 +20411,7 @@
           <t>J | 384呎 (2房)
 $706万
 $18,388/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
           <t>A | 512呎 (3房)
 $1106万
 $21,596/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -20434,7 +20434,7 @@
           <t>B | 374呎 (2房)
 $736万
 $19,690/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20442,7 +20442,7 @@
           <t>C | 560呎 (3房)
 $1146万
 $20,459/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -20450,7 +20450,7 @@
           <t>D | 392呎 (2房)
 $674万
 $17,207/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -20458,7 +20458,7 @@
           <t>E | 391呎 (2房)
 $674万
 $17,240/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -20466,7 +20466,7 @@
           <t>F | 400呎 (2房)
 $684万
 $17,112/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20474,7 +20474,7 @@
           <t>G | 469呎 (2房)
 $807万
 $17,207/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -20482,7 +20482,7 @@
           <t>H | 385呎 (2房)
 $695万
 $18,062/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -20490,7 +20490,7 @@
           <t>J | 384呎 (2房)
 $704万
 $18,331/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
           <t>A | 512呎 (3房)
 $1024万
 $20,004/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20513,7 +20513,7 @@
           <t>B | 374呎 (2房)
 $733万
 $19,588/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -20521,7 +20521,7 @@
           <t>C | 560呎 (3房)
 $1140万
 $20,354/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -20529,7 +20529,7 @@
           <t>D | 392呎 (2房)
 $645万
 $16,449/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>E | 391呎 (2房)
 $672万
 $17,187/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>F | 400呎 (2房)
 $683万
 $17,065/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -20553,7 +20553,7 @@
           <t>G | 469呎 (2房)
 $805万
 $17,162/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -20561,7 +20561,7 @@
           <t>H | 385呎 (2房)
 $682万
 $17,722/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -20569,7 +20569,7 @@
           <t>J | 384呎 (2房)
 $710万
 $18,503/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
           <t>A | 512呎 (3房)
 $978万
 $19,092/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>B | 374呎 (2房)
 $760万
 $20,324/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -20600,7 +20600,7 @@
           <t>C | 560呎 (3房)
 $1088万
 $19,425/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -20608,7 +20608,7 @@
           <t>D | 392呎 (2房)
 $686万
 $17,500/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -20616,7 +20616,7 @@
           <t>E | 391呎 (2房)
 $643万
 $16,435/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -20624,7 +20624,7 @@
           <t>F | 400呎 (2房)
 $653万
 $16,315/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -20632,7 +20632,7 @@
           <t>G | 469呎 (2房)
 $770万
 $16,420/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -20640,7 +20640,7 @@
           <t>H | 385呎 (2房)
 $672万
 $17,444/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -20648,7 +20648,7 @@
           <t>J | 384呎 (2房)
 $680万
 $17,708/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
           <t>A | 512呎 (3房)
 $972万
 $18,994/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -20671,7 +20671,7 @@
           <t>B | 374呎 (2房)
 $756万
 $20,225/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -20679,7 +20679,7 @@
           <t>C | 560呎 (3房)
 $1082万
 $19,330/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -20695,7 +20695,7 @@
           <t>E | 391呎 (2房)
 $641万
 $16,386/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -20703,7 +20703,7 @@
           <t>F | 400呎 (2房)
 $651万
 $16,268/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>G | 469呎 (2房)
 $768万
 $16,380/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>H | 385呎 (2房)
 $646万
 $16,769/呎
-(25年-03月-09日)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -20727,7 +20727,7 @@
           <t>J | 384呎 (2房)
 $667万
 $17,359/呎
-(24年-09月-08日)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
           <t>A | 512呎 (3房)
 $955万
 $18,650/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>B | 374呎 (2房)
 $753万
 $20,123/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20758,7 +20758,7 @@
           <t>C | 560呎 (3房)
 $1149万
 $20,523/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -20766,7 +20766,7 @@
           <t>D | 392呎 (2房)
 $666万
 $17,000/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -20774,7 +20774,7 @@
           <t>E | 391呎 (2房)
 $639万
 $16,338/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -20782,7 +20782,7 @@
           <t>F | 400呎 (2房)
 $649万
 $16,220/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -20790,7 +20790,7 @@
           <t>G | 469呎 (2房)
 $766万
 $16,339/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -20798,7 +20798,7 @@
           <t>H | 385呎 (2房)
 $642万
 $16,686/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -20806,7 +20806,7 @@
           <t>J | 384呎 (2房)
 $650万
 $16,940/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -20821,7 +20821,7 @@
           <t>A | 512呎 (3房)
 $963万
 $18,807/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -20829,7 +20829,7 @@
           <t>B | 374呎 (2房)
 $718万
 $19,203/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -20837,7 +20837,7 @@
           <t>C | 560呎 (3房)
 $1144万
 $20,421/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -20845,7 +20845,7 @@
           <t>D | 392呎 (2房)
 $637万
 $16,255/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -20853,7 +20853,7 @@
           <t>E | 391呎 (2房)
 $637万
 $16,289/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -20861,7 +20861,7 @@
           <t>F | 400呎 (2房)
 $647万
 $16,170/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -20869,7 +20869,7 @@
           <t>G | 469呎 (2房)
 $797万
 $16,991/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -20877,7 +20877,7 @@
           <t>H | 385呎 (2房)
 $639万
 $16,600/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -20885,7 +20885,7 @@
           <t>J | 384呎 (2房)
 $647万
 $16,857/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
           <t>A | 512呎 (3房)
 $999万
 $19,512/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -20908,7 +20908,7 @@
           <t>B | 374呎 (2房)
 $715万
 $19,107/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>C | 560呎 (3房)
 $1066万
 $19,041/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -20924,7 +20924,7 @@
           <t>D | 392呎 (2房)
 $635万
 $16,207/呎
-(24年-08月-21日)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -20932,7 +20932,7 @@
           <t>E | 353呎 (2房)
 $599万
 $16,963/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -20940,7 +20940,7 @@
           <t>F | 400呎 (2房)
 $640万
 $16,008/呎
-(24年-08月-19日)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -20948,7 +20948,7 @@
           <t>G | 469呎 (2房)
 $762万
 $16,256/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -20956,7 +20956,7 @@
           <t>H | 385呎 (2房)
 $636万
 $16,517/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -20964,7 +20964,7 @@
           <t>J | 384呎 (2房)
 $644万
 $16,768/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -21176,7 +21176,7 @@
           <t>B | 380呎 (2房)
 $757万
 $19,924/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -21184,7 +21184,7 @@
           <t>C | 380呎 (2房)
 $791万
 $20,811/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -21192,7 +21192,7 @@
           <t>D | 380呎 (2房)
 $760万
 $19,992/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -21200,7 +21200,7 @@
           <t>E | 380呎 (2房)
 $810万
 $21,318/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -21208,7 +21208,7 @@
           <t>F | 381呎 (2房)
 $818万
 $21,475/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>G | 385呎 (2房)
 $832万
 $21,618/呎
-(24年-09月-11日)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -21224,7 +21224,7 @@
           <t>H | 288呎 (1房)
 $499万
 $17,333/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -21232,7 +21232,7 @@
           <t>J | 272呎 (1房)
 $472万
 $17,335/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -21240,7 +21240,7 @@
           <t>K | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -21248,7 +21248,7 @@
           <t>L | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -21256,7 +21256,7 @@
           <t>M | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -21264,7 +21264,7 @@
           <t>N | 276呎 (1房)
 $459万
 $16,623/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
@@ -21272,7 +21272,7 @@
           <t>P | 274呎 (1房)
 $456万
 $16,624/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -21280,7 +21280,7 @@
           <t>Q | 382呎 (2房)
 $635万
 $16,626/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
           <t>B | 380呎 (2房)
 $760万
 $20,008/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>C | 380呎 (2房)
 $744万
 $19,566/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>D | 380呎 (2房)
 $745万
 $19,600/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>E | 380呎 (2房)
 $794万
 $20,897/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>F | 381呎 (2房)
 $802万
 $21,052/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>G | 385呎 (2房)
 $880万
 $22,857/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -21351,7 +21351,7 @@
           <t>H | 288呎 (1房)
 $469万
 $16,299/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -21359,7 +21359,7 @@
           <t>J | 272呎 (1房)
 $443万
 $16,298/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -21367,7 +21367,7 @@
           <t>K | 276呎 (1房)
 $472万
 $17,112/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -21375,7 +21375,7 @@
           <t>L | 276呎 (1房)
 $450万
 $16,297/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -21383,7 +21383,7 @@
           <t>M | 276呎 (1房)
 $469万
 $16,993/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -21391,7 +21391,7 @@
           <t>N | 276呎 (1房)
 $450万
 $16,297/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="O6" s="20" t="inlineStr">
@@ -21399,7 +21399,7 @@
           <t>P | 274呎 (1房)
 $446万
 $16,296/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="P6" s="20" t="inlineStr">
@@ -21407,7 +21407,7 @@
           <t>Q | 382呎 (2房)
 $623万
 $16,298/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21422,7 @@
           <t>A | 385呎 (2房)
 $751万
 $19,501/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>B | 380呎 (2房)
 $770万
 $20,266/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -21438,7 +21438,7 @@
           <t>C | 380呎 (2房)
 $740万
 $19,471/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -21446,7 +21446,7 @@
           <t>D | 380呎 (2房)
 $773万
 $20,337/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -21454,7 +21454,7 @@
           <t>E | 380呎 (2房)
 $820万
 $21,576/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -21462,7 +21462,7 @@
           <t>F | 381呎 (2房)
 $794万
 $20,845/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -21470,7 +21470,7 @@
           <t>G | 385呎 (2房)
 $808万
 $20,984/呎
-(24年-09月-08日)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -21478,7 +21478,7 @@
           <t>H | 288呎 (1房)
 $467万
 $16,219/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -21486,7 +21486,7 @@
           <t>J | 272呎 (1房)
 $441万
 $16,217/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -21494,7 +21494,7 @@
           <t>K | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -21502,7 +21502,7 @@
           <t>L | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -21510,7 +21510,7 @@
           <t>M | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -21518,7 +21518,7 @@
           <t>N | 276呎 (1房)
 $448万
 $16,214/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -21526,7 +21526,7 @@
           <t>P | 274呎 (1房)
 $463万
 $16,909/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
@@ -21534,7 +21534,7 @@
           <t>Q | 382呎 (2房)
 $620万
 $16,220/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -21549,7 +21549,7 @@
           <t>A | 385呎 (2房)
 $919万
 $23,868/呎
-(26年-07月-02日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -21557,7 +21557,7 @@
           <t>B | 380呎 (2房)
 $735万
 $19,337/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -21565,7 +21565,7 @@
           <t>C | 380呎 (2房)
 $768万
 $20,203/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -21573,7 +21573,7 @@
           <t>D | 380呎 (2房)
 $769万
 $20,237/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -21581,7 +21581,7 @@
           <t>E | 380呎 (2房)
 $785万
 $20,661/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -21589,7 +21589,7 @@
           <t>F | 381呎 (2房)
 $793万
 $20,811/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -21597,7 +21597,7 @@
           <t>G | 385呎 (2房)
 $804万
 $20,881/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -21605,7 +21605,7 @@
           <t>H | 288呎 (1房)
 $465万
 $16,135/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -21613,7 +21613,7 @@
           <t>J | 272呎 (1房)
 $439万
 $16,136/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -21621,7 +21621,7 @@
           <t>K | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -21629,7 +21629,7 @@
           <t>L | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -21637,7 +21637,7 @@
           <t>M | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -21645,7 +21645,7 @@
           <t>N | 276呎 (1房)
 $445万
 $16,134/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -21653,7 +21653,7 @@
           <t>P | 274呎 (1房)
 $442万
 $16,135/呎
-(24年-08月-07日)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -21661,7 +21661,7 @@
           <t>Q | 382呎 (2房)
 $616万
 $16,139/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21676,7 @@
           <t>A | 385呎 (2房)
 $743万
 $19,309/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -21684,7 +21684,7 @@
           <t>B | 380呎 (2房)
 $762万
 $20,063/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -21692,7 +21692,7 @@
           <t>C | 380呎 (2房)
 $764万
 $20,100/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -21700,7 +21700,7 @@
           <t>D | 380呎 (2房)
 $734万
 $19,308/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -21708,7 +21708,7 @@
           <t>E | 380呎 (2房)
 $768万
 $20,218/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -21716,7 +21716,7 @@
           <t>F | 381呎 (2房)
 $776万
 $20,373/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -21724,7 +21724,7 @@
           <t>G | 385呎 (2房)
 $797万
 $20,704/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -21732,7 +21732,7 @@
           <t>H | 251呎 (1房)
 $416万
 $16,558/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -21740,7 +21740,7 @@
           <t>J | 234呎 (1房)
 $386万
 $16,513/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -21748,7 +21748,7 @@
           <t>K | 238呎 (1房)
 $396万
 $16,618/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -21756,7 +21756,7 @@
           <t>L | 239呎 (1房)
 $396万
 $16,590/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -21764,7 +21764,7 @@
           <t>M | 239呎 (1房)
 $396万
 $16,590/呎
-(24年-08月-01日)</t>
+(24年-08月-02日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -21772,7 +21772,7 @@
           <t>N | 238呎 (1房)
 $412万
 $17,328/呎
-(24年-07月-31日)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -21780,7 +21780,7 @@
           <t>P | 236呎 (1房)
 $408万
 $17,297/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -21788,7 +21788,7 @@
           <t>Q | 345呎 (2房)
 $648万
 $18,768/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -2769,38 +2769,30 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>8664000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>22159</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="5" t="n">
+        <v>8664000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>22159</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2809,7 +2801,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18988,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19006,7 +18998,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19347,12 +19339,12 @@
 (25年-08月-29日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
-招标单位
--
-(在售)</t>
+$866万
+$22,159/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -642,7 +642,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -3871,31 +3871,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>8301000</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>20752</v>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>6806820</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>17017</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9211,31 +9219,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="5" t="n">
-        <v>12295000</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>24014</v>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>10081900</v>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v>19691</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12373,31 +12389,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>7818000</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>19944</v>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K188" s="5" t="n">
-        <v>6410760</v>
-      </c>
-      <c r="L188" s="5" t="n">
-        <v>16354</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15163,31 +15187,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="5" t="n">
-        <v>9389000</v>
-      </c>
-      <c r="I233" s="5" t="n">
-        <v>24387</v>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K233" s="5" t="n">
-        <v>7698980</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>19997</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16093,31 +16125,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="5" t="n">
-        <v>9204000</v>
-      </c>
-      <c r="I248" s="5" t="n">
-        <v>23906</v>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K248" s="5" t="n">
-        <v>7547280</v>
-      </c>
-      <c r="L248" s="5" t="n">
-        <v>19603</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19508,8 +19548,8 @@
       <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-$830万
-$20,752/呎
+招标单位
+-
 (在售)</t>
         </is>
       </c>
@@ -20179,8 +20219,8 @@
       <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1230万
-$24,014/呎
+招标单位
+-
 (在售)</t>
         </is>
       </c>
@@ -20677,8 +20717,8 @@
       <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
-$782万
-$19,944/呎
+招标单位
+-
 (在售)</t>
         </is>
       </c>
@@ -21158,8 +21198,8 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
-$939万
-$24,387/呎
+招标单位
+-
 (在售)</t>
         </is>
       </c>
@@ -21285,8 +21325,8 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
-$920万
-$23,906/呎
+招标单位
+-
 (在售)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -3475,38 +3475,30 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>14052000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>25093</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K45" s="5" t="n">
+        <v>14052000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>25093</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3515,7 +3507,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19028,7 +19020,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19038,7 +19030,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19442,12 +19434,12 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-招标单位
--
-(在售)</t>
+$1405万
+$25,093/呎
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -1131,38 +1131,30 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>16408000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>29300</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K9" s="5" t="n">
+        <v>16408000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>29300</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1163,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3855,38 +3847,30 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>8712000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>21780</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="5" t="n">
+        <v>8712000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>21780</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3879,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19004,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19030,7 +19014,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19118,7 +19102,86 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$1641万
+$29,300/呎
+(26年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 392呎 (2房)
+$744万
+$18,974/呎
+(25年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$725万
+$18,550/呎
+(25年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 400呎 (2房)
+$702万
+$17,562/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 469呎 (2房)
+$1079万
+$23,000/呎
+(25年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$887万
+$23,039/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 384呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 374呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -19126,47 +19189,47 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
-$744万
-$18,974/呎
-(25年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+$736万
+$18,783/呎
+(25年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
-$725万
-$18,550/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
+$703万
+$17,974/呎
+(24年-08月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-$702万
-$17,562/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
+$689万
+$17,220/呎
+(24年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
-$1079万
-$23,000/呎
-(25年-09月-18日)</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+$844万
+$18,000/呎
+(25年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
-$887万
-$23,039/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+$821万
+$21,330/呎
+(25年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -19175,13 +19238,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -19189,7 +19252,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -19197,7 +19260,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -19205,47 +19268,47 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
-$736万
-$18,783/呎
-(25年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
+$729万
+$18,594/呎
+(25年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
-$703万
-$17,974/呎
-(24年-08月-02日)</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
+$701万
+$17,921/呎
+(24年-08月-01日)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-$689万
-$17,220/呎
-(24年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+$687万
+$17,168/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
-$844万
-$18,000/呎
-(25年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+$832万
+$17,731/呎
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
-$821万
-$21,330/呎
-(25年-10月-24日)</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
+$852万
+$22,143/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -19254,13 +19317,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -19268,7 +19331,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
 招标单位
@@ -19276,7 +19339,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
 招标单位
@@ -19284,47 +19347,47 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
-$729万
-$18,594/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+$722万
+$18,406/呎
+(25年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
-$701万
-$17,921/呎
-(24年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
+$866万
+$22,159/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-$687万
-$17,168/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
+$685万
+$17,118/呎
+(24年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
-$832万
-$17,731/呎
-(25年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+$819万
+$17,465/呎
+(25年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
-$852万
-$22,143/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
+$789万
+$20,501/呎
+(25年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
 招标单位
@@ -19333,13 +19396,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -19347,78 +19410,78 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
+$885万
+$23,663/呎
+(25年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 560呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
+$1405万
+$25,093/呎
+(26年-08月-13日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 392呎 (2房)
-$722万
-$18,406/呎
-(25年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+$721万
+$18,403/呎
+(24年-09月-03日)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 391呎 (2房)
-$866万
-$22,159/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+$697万
+$17,816/呎
+(24年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-$685万
-$17,118/呎
-(24年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+$683万
+$17,065/呎
+(24年-08月-02日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 469呎 (2房)
-$819万
-$17,465/呎
-(25年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+$817万
+$17,416/呎
+(24年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 385呎 (2房)
-$789万
-$20,501/呎
-(25年-10月-28日)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
+$742万
+$19,286/呎
+(25年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 384呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+$752万
+$19,578/呎
+(25年-08月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 招标单位
@@ -19426,85 +19489,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 374呎 (2房)
-$885万
-$23,663/呎
-(25年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 560呎 (3房)
-$1405万
-$25,093/呎
-(26年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 392呎 (2房)
-$721万
-$18,403/呎
-(24年-09月-03日)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$697万
-$17,816/呎
-(24年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>F | 400呎 (2房)
-$683万
-$17,065/呎
-(24年-08月-02日)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>G | 469呎 (2房)
-$817万
-$17,416/呎
-(24年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$742万
-$19,286/呎
-(25年-09月-04日)</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>J | 384呎 (2房)
-$752万
-$19,578/呎
-(25年-08月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 374呎 (2房)
@@ -19537,12 +19521,12 @@
 (24年-08月-09日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
-招标单位
--
-(在售)</t>
+$871万
+$21,780/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
